--- a/EstablecimientoSalud/excels/CAJAMARCA-CHOTA-CHOTA.xlsx
+++ b/EstablecimientoSalud/excels/CAJAMARCA-CHOTA-CHOTA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,12 +493,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>23433</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>60401</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,27 +513,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>QUEROCOTO</t>
+          <t>CHOTA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.35102559</t>
+          <t>-6.558193</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.12695948</t>
+          <t>-78.6483843</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Centro Medico La Granja</t>
+          <t>POSTA MEDICA POLICIAL CHOTA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CAMINO RURAL Campamento Minero La GranjaN° 0 PISO 0 DEPARTAMENTO 0 INTERIOR 0 MANZANA 0 LOTE 0 KILOMETRO 0 URBANIZACION 0 DISTRITO QUEROCOTO PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>AVENIDA AV.INCA GARCILAZO DE LA VEGA 724 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26317</t>
+          <t>18547</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,27 +580,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.56132045</t>
+          <t>-6.5617701</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-78.64723578</t>
+          <t>-78.65090622</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO CHOTA</t>
+          <t>PUESTO DE SALUD "CHOTA"</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Jr. GREGORIO MALCA N° 1043 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>AVENIDA INCA GARCILAZO DE LA VEGAN° 235 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -617,12 +617,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>25508</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>60401</t>
+          <t>60419</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -637,32 +637,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CHOTA</t>
+          <t>CHALAMARCA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.55930065</t>
+          <t>-6.43910064</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-78.65136639</t>
+          <t>-78.52719137</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>POLICLINICO SAN JUAN EIRL</t>
+          <t>CENTRO PALMA</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jr. ADRIANO NOVOA 299 A UNA CUADRA DEL MERCADO MAYORISTA CHOTA CHOTA CAJAMARCA</t>
+          <t>OTROS CENTRO POBLADO CENTRO PALMA SN TACABAMBA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLOGICO BRIDENT</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO RENACER</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Jr. CAJAMARCAN° 758 PISO 2 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>CALLE ACCESO ALBERGUE INFANTIL A CINCUENTA METROS DEL PARQUE INFANTIL SANTA EULALIA. CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>I-1</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>33505</t>
+          <t>6842</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.5620221</t>
+          <t>-6.62654</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-78.65019479</t>
+          <t>-78.62297</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CONSULTORIO ODONTOLOGICOS PRODENT</t>
+          <t>SILLEROPATA ALTO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AVENIDA INCA GARCILAZO DE LA VEGAN° 111 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD SILLEROPANTA ALTO COMUNIDAD SILLEROPANTA ALTO CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>36211</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,22 +828,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.56198213</t>
+          <t>-6.60321</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-78.64787736</t>
+          <t>-78.66489</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Centro MA©dico MUNDO SALUD</t>
+          <t>CABRACANCHA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jr. SANTA ROSAN° 384 PISO 1 DEPARTAMENTO 1 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD CABRACANCHA COMUNIDAD CABRACANCHA CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>36241</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.558193</t>
+          <t>-6.55439</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-78.6483843</t>
+          <t>-78.59715</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>POLICLINICO TABOADA</t>
+          <t>EL MIRADOR (CHOTA)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Jr. GREGORIO MALCAN° 985 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD MIRADOR COMUNIDAD MIRADOR CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.558193</t>
+          <t>-6.58527</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-78.6483843</t>
+          <t>-78.60454</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>POSTA MEDICA POLICIAL CHOTA</t>
+          <t>NUEVO ORIENTE</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AVENIDA AV.INCA GARCILAZO DE LA VEGA 724 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD NUEVO ORIENTE COMUNIDAD NUEVO ORIENTE CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18547</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.5617701</t>
+          <t>-6.490094</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-78.65090622</t>
+          <t>-78.62355414</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>PUESTO DE SALUD "CHOTA"</t>
+          <t>LIBERTAD LA PALMA</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AVENIDA INCA GARCILAZO DE LA VEGAN° 235 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS CENTRO POBLADO LIBERTAD LA PALMA CENTRO POBLADO LIBERTAD LA PALMA SOCOTA CUTERVO CAJAMARCA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>33814</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.56031461</t>
+          <t>-6.52985</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-78.64429311</t>
+          <t>-78.637</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO ESPECIALIZADO SANTISIMA VIRGEN DE LA PUERTA</t>
+          <t>COLPATUAPAMPA</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AVENIDA TACABAMBAN° 344 PISO 1 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD COLPATUAPAMPA COMUNIDAD COLPATUAPAMPA CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.56055015</t>
+          <t>-6.51086</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-78.64549613</t>
+          <t>-78.6121</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CENTRO MEDICO GINECOLAGICO SAN FERNANDO</t>
+          <t>CONDORPULLANA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PASAJE JUAN XXIII 244 246 1 FRENTE A LA CAPILLA SANTA ROSA CHOTA CHOTA CAJAMARCA</t>
+          <t>OTROS COMUNIDAD CONDORPULLANA COMUNIDAD CONDORPULLANA CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>60401</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CHALAMARCA</t>
+          <t>CHOTA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.43910064</t>
+          <t>-6.62262</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-78.52719137</t>
+          <t>-78.67043</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CENTRO PALMA</t>
+          <t>PAMPA LA LAGUNA</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>OTROS CENTRO POBLADO CENTRO PALMA SN TACABAMBA CHOTA CAJAMARCA</t>
+          <t>OTROS COMUNIDAD PAMPA LA LAGUNA DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1262,27 +1262,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.558193</t>
+          <t>-6.50458008</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-78.6483843</t>
+          <t>-78.65886719</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO RENACER</t>
+          <t>UTCHUCLACHULIT</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CALLE ACCESO ALBERGUE INFANTIL A CINCUENTA METROS DEL PARQUE INFANTIL SANTA EULALIA. CHOTA CHOTA CAJAMARCA</t>
+          <t>OTROS CASERIO DE UTCHUCLACHULIT CASERIO DE UTCHUCLACHULIT CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27327</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1324,22 +1324,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.558193</t>
+          <t>-6.49014296</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-78.6483843</t>
+          <t>-78.62355714</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CENTRO ODONTOLOGICO PARMEB</t>
+          <t>LA PALMA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jr. EXEQUIEL MONTOYAN° 109 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD LA PALMA DISTRITO CONCHAN PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>6928</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1386,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.56148651</t>
+          <t>-6.6290033</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-78.64876249</t>
+          <t>-78.59521099</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CONSULTORIO DENTAL LIMA SUR</t>
+          <t>NINO JESUS</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Jr. 30 agosto 374 una cuadra de plaza principal CHOTA CHOTA CAJAMARCA</t>
+          <t>OTROS COMUNIDAD GRUTAS DE NEGROPAMPA COMUNIDAD GRUTAS DE NEGROPAMPA CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>34462</t>
+          <t>4671</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,27 +1448,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.55996721</t>
+          <t>-6.58883232</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-78.65389781</t>
+          <t>-78.68985703</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CENTRO DE ESPECIALIDADES MADICAS GLOBAL MEDIC S.A.C.</t>
+          <t>LANCHEBAMBA</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Jr. 30 DE AGOSTO 1015 CHOTA CHOTA CAJAMARCA</t>
+          <t>OTROS COMUNIDAD DE LANCHEBAMBA COMUNIDAD DE LANCHEBAMBA CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>33497</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,35 +1510,1151 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.56042065</t>
+          <t>-6.55815756</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-78.64772448</t>
+          <t>-78.63490914</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CONSULTORIO DENTAL MI SONRISA</t>
+          <t>SANTA ROSA BAJO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Jr. ADRIANO NOVOAN° 626 PISO 1 DISTRITO CHOTA PROVINCIA CHOTA DEPARTAMENTO CAJAMARCA</t>
+          <t>OTROS COMUNIDAD SANTA ROSA BAJO COMUNIDAD SANTA ROSA BAJO CHOTA CHOTA CAJAMARCA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6926</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-6.55828</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-78.593</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PROGRESO PAMPA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD PROGRESOPAMPA COMUNIDAD PROGRESOPAMPA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>I-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-6.57858</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-78.67141</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>IRACA GRANDE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD IRACA GRANDE COMUNIDAD IRACA GRANDE CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-6.60337</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-78.68218</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>SAN ANTONIO DE IRACA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD SAN ANTONIO DE IRACA COMUNIDAD SAN ANTONIO DE IRACA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>6957</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-6.5059</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-78.67257</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SARABAMBA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD SARABAMBA COMUNIDAD SARABAMBA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4660</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-6.56244532</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-78.64738403</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PATRONA DE CHOTA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>OTROS CIUDAD DE CHOTA CIUDAD DE CHOTA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-6.59449</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-78.5878</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CHAUPELANCHE</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD CHAUPELANCHE COMUNIDAD CHAUPELANCHE CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4668</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-6.62635</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-78.6115</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CUYUMALCA</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD CUYUMALCA COMUNIDAD CUYUMALCA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4664</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-6.50985</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-78.644</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CHULIT</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD CHULIT ALTO COMUNIDAD CHULIT ALTO CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7710</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-6.63206</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-78.64228</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LINGAN GRANDE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD LINGAN GRANDE COMUNIDAD LINGAN GRANDE CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-6.51741</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-78.70014</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CHUYABAMBA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD DE CHUYABAMBA COMUNIDAD DE CHUYABAMBA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-6.5488</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-78.61562</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ROJASPAMPA</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD ROJASPAMPA COMUNIDAD ROJASPAMPA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-6.51673</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-78.66495</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>SIVINGAN ALTO</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD SIVIGAN ALTO COMUNIDAD SIVIGAN ALTO CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-6.51551797</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-78.66115686</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>TUNEL CONCHANO</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>OTROS EL CAMPAMENTO TUNEL CONCHANO EL CAMPAMENTO TUNEL CONCHANO CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4672</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-6.61006</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-78.61987</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>NEGROPAMPA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD NEGROPAMPA COMUNIDAD NEGROPAMPA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4678</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-6.63061</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-78.63455</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SILLEROPATA BAJO</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD SILLEROPATA BAJO COMUNIDAD SILLEROPATA BAJO CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4681</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-6.6045</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-78.64762</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>SOILA VICTORIA NUNEZ SALDANA - YURACYACU</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD YURACYACU COMUNIDAD YURACYACU CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10880</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-6.54734961</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-78.65011914</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>RAMBRAMPATA</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD RAMBRAMPATA COMUNIDAD RAMBRAMPATA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>060401</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6955</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>60401</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-6.62219</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-78.65159</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>LINGAN PATA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>OTROS COMUNIDAD LINGAN PATA COMUNIDAD LINGAN PATA CHOTA CHOTA CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>I-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>060401</t>
         </is>

--- a/EstablecimientoSalud/excels/CAJAMARCA-CHOTA-CHOTA.xlsx
+++ b/EstablecimientoSalud/excels/CAJAMARCA-CHOTA-CHOTA.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>10929</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.558193</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>18547</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.5617701</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>25508</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>60419</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CHALAMARCA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.43910064</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>26186</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.558193</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>6842</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-6.62654</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>4661</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-6.60321</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>4669</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.55439</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>4673</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-6.58527</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>11063</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-6.490094</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>4666</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-6.52985</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>4667</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-6.51086</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>4674</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-6.62262</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>10991</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-6.50458008</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>4762</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-6.49014296</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>6928</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-6.6290033</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>4671</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-6.58883232</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>4675</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-6.55815756</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>6926</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-6.55828</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>4670</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-6.57858</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>4677</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-6.60337</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>6957</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-6.5059</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>4660</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-6.56244532</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>4663</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-6.59449</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>4668</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-6.62635</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>4664</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-6.50985</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>7710</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-6.63206</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>4665</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-6.51741</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>4676</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-6.5488</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>4679</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-6.51673</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>4680</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-6.51551797</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>4672</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-6.61006</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>4678</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-6.63061</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>4681</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-6.6045</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>10880</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-6.54734961</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>060401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CAJAMARCA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CHOTA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>6955</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>60401</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CAJAMARCA</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>CHOTA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-6.62219</t>
@@ -2652,11 +2477,6 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>060401</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/CAJAMARCA-CHOTA-CHOTA.xlsx
+++ b/EstablecimientoSalud/excels/CAJAMARCA-CHOTA-CHOTA.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
